--- a/ISOC_result/My_room_11/My_room_11_result.xlsx
+++ b/ISOC_result/My_room_11/My_room_11_result.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ISOC_result\My_room_11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ISOC\ISOC_result\My_room_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040D0A1A-F872-4929-B288-4067E918FC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183FF8C5-6D05-401E-AE2B-ED97240C3230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8F062009-FD71-4F10-8C79-40340D4D7484}"/>
   </bookViews>
@@ -135,14 +135,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,14 +526,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -548,7 +548,7 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -566,7 +566,7 @@
         <v>4507.37</v>
       </c>
       <c r="D3" s="4">
-        <v>720.14</v>
+        <v>407.63</v>
       </c>
       <c r="E3" s="4">
         <v>44811</v>
@@ -586,7 +586,7 @@
         <v>4476.6499999999996</v>
       </c>
       <c r="D4" s="4">
-        <v>969.77</v>
+        <v>334.44</v>
       </c>
       <c r="E4" s="4">
         <v>45151</v>
@@ -627,7 +627,7 @@
         <v>4730.5</v>
       </c>
       <c r="D6" s="2">
-        <v>894.82</v>
+        <v>263.77</v>
       </c>
       <c r="E6" s="4">
         <v>45868</v>
@@ -1227,7 +1227,7 @@
         <v>4769.34</v>
       </c>
       <c r="D36" s="2">
-        <v>814.57</v>
+        <v>340.73</v>
       </c>
       <c r="E36" s="4">
         <v>46613</v>
@@ -1267,7 +1267,7 @@
         <v>4680.93</v>
       </c>
       <c r="D38" s="2">
-        <v>701.42</v>
+        <v>319.45999999999998</v>
       </c>
       <c r="E38" s="4">
         <v>46120</v>
@@ -1287,7 +1287,7 @@
         <v>4773.2700000000004</v>
       </c>
       <c r="D39" s="2">
-        <v>871.91</v>
+        <v>314.12</v>
       </c>
       <c r="E39" s="4">
         <v>45787</v>
@@ -1307,7 +1307,7 @@
         <v>4788.88</v>
       </c>
       <c r="D40" s="4">
-        <v>1340.73</v>
+        <v>300.91000000000003</v>
       </c>
       <c r="E40" s="4">
         <v>45911</v>
@@ -1407,7 +1407,7 @@
         <v>5049.74</v>
       </c>
       <c r="D45" s="2">
-        <v>768.64</v>
+        <v>224.28</v>
       </c>
       <c r="E45" s="4">
         <v>45845</v>
